--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488097_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488097_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1813</v>
+        <v>4.7018</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3561</v>
+        <v>3.1148</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8252</v>
+        <v>1.587</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5495</v>
+        <v>3.8993</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4248</v>
+        <v>1.8676</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1247</v>
+        <v>2.0317</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3484</v>
+        <v>2.9641</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8618</v>
+        <v>1.6344</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4866</v>
+        <v>1.3298</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2011</v>
+        <v>0.9351</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5629</v>
+        <v>0.2332</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3619</v>
+        <v>0.7019</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7002</v>
+        <v>0.6836</v>
       </c>
       <c r="T2" t="n">
-        <v>4.4567</v>
+        <v>0.6086</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2435</v>
+        <v>0.075</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2666</v>
+        <v>-0.674</v>
       </c>
       <c r="W2" t="n">
         <v>0.5331</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7997</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8293</v>
+        <v>4.5285</v>
       </c>
       <c r="E3" t="n">
-        <v>2.631</v>
+        <v>2.8717</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1983</v>
+        <v>1.6568</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9315</v>
+        <v>2.5495</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8824</v>
+        <v>1.4248</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0491</v>
+        <v>1.1247</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7457</v>
+        <v>2.3484</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3234</v>
+        <v>0.8618</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4223</v>
+        <v>1.4866</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1857</v>
+        <v>0.2011</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5629</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3733</v>
+        <v>-0.3619</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1377</v>
+        <v>2.0474</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4444</v>
+        <v>1.9724</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3066</v>
+        <v>0.075</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1476</v>
+        <v>-0.2666</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4142</v>
+        <v>0.5331</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2666</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8287</v>
+        <v>4.3523</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0732</v>
+        <v>2.7328</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7555</v>
+        <v>1.6195</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8993</v>
+        <v>2.9315</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8676</v>
+        <v>0.8824</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0317</v>
+        <v>2.0491</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9641</v>
+        <v>2.7457</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6344</v>
+        <v>0.3234</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3298</v>
+        <v>2.4223</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9351</v>
+        <v>0.1857</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2332</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7019</v>
+        <v>-0.3733</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7929</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R4" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1895</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.433</v>
+        <v>0.5462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2435</v>
+        <v>0.1145</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.674</v>
+        <v>2.1476</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5331</v>
+        <v>2.4142</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERRERA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9925</v>
+        <v>3.0358</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1565</v>
+        <v>0.9077</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.164</v>
+        <v>2.1282</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7377</v>
+        <v>1.5191</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1944</v>
+        <v>2.0645</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5433</v>
+        <v>-0.5454</v>
       </c>
       <c r="J5" t="n">
-        <v>1.594</v>
+        <v>0.9277</v>
       </c>
       <c r="K5" t="n">
-        <v>1.594</v>
+        <v>1.3657</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.4381</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1437</v>
+        <v>0.5914</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3996</v>
+        <v>0.6988</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5433</v>
+        <v>-0.1073</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9882</v>
+        <v>0.8011</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2959</v>
+        <v>-0.02</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3076</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2666</v>
+        <v>-0.8701</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8252</v>
+        <v>2.2337</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1734</v>
+        <v>2.3415</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9986</v>
+        <v>-0.1078</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5191</v>
+        <v>1.7377</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0645</v>
+        <v>1.1944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5454</v>
+        <v>0.5433</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9277</v>
+        <v>1.594</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3657</v>
+        <v>1.594</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4381</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5914</v>
+        <v>0.1437</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6988</v>
+        <v>-0.3996</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1073</v>
+        <v>0.5433</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5904</v>
+        <v>0.2294</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1011</v>
+        <v>0.4809</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6915</v>
+        <v>-0.2515</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8701</v>
+        <v>0.2666</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0799</v>
+        <v>1.9451</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1181</v>
+        <v>-0.7236</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0383</v>
+        <v>2.6687</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5477</v>
+        <v>-0.0776</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8667</v>
+        <v>-0.6728</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.5952</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2354</v>
+        <v>-0.3411</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1148</v>
+        <v>-0.7662</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>0.4251</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3123</v>
+        <v>0.2635</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2481</v>
+        <v>0.0934</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5604</v>
+        <v>0.17</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5322</v>
+        <v>0.6946</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8561</v>
+        <v>0.6086</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3239</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.4142</v>
+        <v>0.337</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4142</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4399</v>
+        <v>1.0031</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1727</v>
+        <v>1.8168</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6125</v>
+        <v>-0.8136</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0776</v>
+        <v>3.5477</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6728</v>
+        <v>2.8667</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5952</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3411</v>
+        <v>3.2354</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7662</v>
+        <v>3.1148</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4251</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2635</v>
+        <v>0.3123</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0934</v>
+        <v>-0.2481</v>
       </c>
       <c r="O8" t="n">
-        <v>0.17</v>
+        <v>0.5604</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9911</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8106</v>
+        <v>1.4555</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8405</v>
+        <v>1.5548</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0299</v>
+        <v>-0.0993</v>
       </c>
       <c r="V8" t="n">
-        <v>0.337</v>
+        <v>-2.4142</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.337</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8153</v>
+        <v>-2.5624</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.9715</v>
+        <v>-5.196</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1562</v>
+        <v>2.6335</v>
       </c>
       <c r="G9" t="n">
         <v>0.6268</v>
@@ -1156,13 +1156,13 @@
         <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9335</v>
+        <v>0.3193</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2972</v>
+        <v>0.4783</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6363</v>
+        <v>-0.159</v>
       </c>
       <c r="V9" t="n">
         <v>-0.337</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.5728</v>
+        <v>-5.8254</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8502</v>
+        <v>-4.0748</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7226</v>
+        <v>-1.7507</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2209</v>
@@ -1234,13 +1234,13 @@
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4996</v>
+        <v>0.2478</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1762</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3235</v>
+        <v>-0.3515</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4737</v>
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.7887</v>
+        <v>13.4125</v>
       </c>
       <c r="E11" t="n">
-        <v>3.167099999999999</v>
+        <v>3.790899999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>9.621400000000001</v>
+        <v>9.621599999999999</v>
       </c>
       <c r="G11" t="n">
         <v>14.5131</v>
       </c>
       <c r="H11" t="n">
-        <v>9.759199999999998</v>
+        <v>9.7592</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7539</v>
+        <v>4.753900000000001</v>
       </c>
       <c r="J11" t="n">
         <v>11.3918</v>
       </c>
       <c r="K11" t="n">
-        <v>8.224100000000002</v>
+        <v>8.2241</v>
       </c>
       <c r="L11" t="n">
         <v>3.1675</v>
@@ -1312,13 +1312,13 @@
         <v>12.8846</v>
       </c>
       <c r="S11" t="n">
-        <v>6.5155</v>
+        <v>7.1395</v>
       </c>
       <c r="T11" t="n">
-        <v>6.2051</v>
+        <v>6.8291</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3105</v>
+        <v>0.3103000000000002</v>
       </c>
       <c r="V11" t="n">
         <v>-3.2844</v>
@@ -1327,13 +1327,13 @@
         <v>3.41</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.6944</v>
+        <v>-6.694400000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>N. PEÑA BAÑOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.3312</v>
+        <v>1.8107</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9782</v>
+        <v>1.8107</v>
       </c>
       <c r="F12" t="n">
-        <v>0.353</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1338</v>
+        <v>1.8107</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5132</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6206</v>
+        <v>1.2053</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5171</v>
+        <v>1.8107</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6001</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1172</v>
+        <v>1.2053</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6167</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1133</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5034</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2073</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3497</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1424</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. PEÑA BAÑOS</t>
+          <t>A. GONZALEZ PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8107</v>
+        <v>1.0222</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8107</v>
+        <v>0.3582</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8107</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.4941</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2053</v>
+        <v>-2.1387</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8107</v>
+        <v>0.7004</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.1999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2053</v>
+        <v>-1.4995</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-1.3451</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.7058</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-0.6392</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0.6681</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.3668</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0.3013</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.0068</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7653</v>
+        <v>0.5295</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5055</v>
+        <v>0.2464</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2598</v>
+        <v>0.2831</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.8414</v>
+        <v>-2.1338</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.5969</v>
+        <v>-0.5132</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7556</v>
+        <v>-1.6206</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3412</v>
+        <v>-0.5171</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.0683</v>
+        <v>0.6001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7271</v>
+        <v>-1.1172</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5001</v>
+        <v>-1.6167</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5286</v>
+        <v>-1.1133</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0285</v>
+        <v>-0.5034</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7751</v>
+        <v>1.3876</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7751</v>
+        <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0981</v>
+        <v>0.4057</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8468</v>
+        <v>0.6179</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7487</v>
+        <v>-0.2123</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2666</v>
+        <v>0.8701</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X14" t="n">
         <v>-0.2666</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PEREZ</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.249</v>
+        <v>0.3672</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4568</v>
+        <v>0.0794</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7058</v>
+        <v>0.2878</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-1.8414</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4941</v>
+        <v>-2.5969</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1387</v>
+        <v>0.7556</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7004</v>
+        <v>-0.3412</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1999</v>
+        <v>-1.0683</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4995</v>
+        <v>0.7271</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3451</v>
+        <v>-1.5001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7058</v>
+        <v>-1.5286</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6392</v>
+        <v>0.0285</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5947</v>
+        <v>2.7751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5769</v>
+        <v>2.7751</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4413</v>
+        <v>-0.3</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1818</v>
+        <v>0.4206</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2595</v>
+        <v>-0.7206</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7403</v>
+        <v>-0.2666</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0068</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>-0.2666</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3924</v>
+        <v>-0.1828</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.197</v>
+        <v>-0.0951</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1954</v>
+        <v>-0.0877</v>
       </c>
       <c r="G16" t="n">
         <v>0.5373</v>
@@ -1702,13 +1702,13 @@
         <v>1.3876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.551</v>
+        <v>-0.3414</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3634</v>
+        <v>-0.2615</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1876</v>
+        <v>-0.0799</v>
       </c>
       <c r="V16" t="n">
         <v>1.2071</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>A. CONTRERAS RUBINO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1265</v>
+        <v>-1.3786</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8615</v>
+        <v>-1.2249</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.265</v>
+        <v>-0.1536</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4258</v>
+        <v>-3.6057</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6969</v>
+        <v>-0.6634</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7289</v>
+        <v>-2.9423</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5584</v>
+        <v>-2.6222</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0404</v>
+        <v>0.7333</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5988</v>
+        <v>-3.3555</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-0.9836</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7372</v>
+        <v>-1.3967</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1301</v>
+        <v>0.4132</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7007</v>
+        <v>0.0973</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.312</v>
+        <v>0.1901</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3888</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9405</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GUINDO CASTILLO</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2623</v>
+        <v>-1.8947</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1674</v>
+        <v>-1.6578</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0949</v>
+        <v>-0.2369</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9447</v>
+        <v>-1.4258</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.629</v>
+        <v>-0.6969</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3157</v>
+        <v>-0.7289</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5515</v>
+        <v>-0.5584</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6319</v>
+        <v>0.0404</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0804</v>
+        <v>-0.5988</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3932</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9971</v>
+        <v>-0.7372</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3961</v>
+        <v>-0.1301</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5664</v>
+        <v>-0.4689</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1176</v>
+        <v>-0.1082</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6839</v>
+        <v>-0.3607</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBINO</t>
+          <t>P. GUINDO CASTILLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.347</v>
+        <v>-2.0317</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1418</v>
+        <v>-0.2692</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2052</v>
+        <v>-1.7625</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.6057</v>
+        <v>-1.9447</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6634</v>
+        <v>-1.629</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.9423</v>
+        <v>-0.3157</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.6222</v>
+        <v>-0.5515</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7333</v>
+        <v>-0.6319</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.3555</v>
+        <v>0.0804</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9836</v>
+        <v>-1.3932</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3967</v>
+        <v>-0.9971</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4132</v>
+        <v>-0.3961</v>
       </c>
       <c r="P19" t="n">
         <v>1.1893</v>
@@ -1936,22 +1936,22 @@
         <v>1.1893</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8711</v>
+        <v>-0.3359</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7267</v>
+        <v>0.0157</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1444</v>
+        <v>-0.3515</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9405</v>
+        <v>-0.9405</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9182</v>
+        <v>-2.7091</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.122</v>
+        <v>-3.7977</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2038</v>
+        <v>1.0886</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7462</v>
@@ -2014,13 +2014,13 @@
         <v>3.1716</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.749</v>
+        <v>-1.5399</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.7875</v>
+        <v>-0.4632</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.9615</v>
+        <v>-1.0767</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6036</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.8983</v>
+        <v>-6.2839</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.9695</v>
+        <v>-5.0714</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9288</v>
+        <v>-1.2125</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5187</v>
@@ -2092,13 +2092,13 @@
         <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9415</v>
+        <v>-1.327</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.253</v>
+        <v>-0.3549</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.6884</v>
+        <v>-0.9721</v>
       </c>
       <c r="V21" t="n">
         <v>0.337</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-12.7885</v>
+        <v>-10.7512</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.621599999999999</v>
+        <v>-9.6214</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1669</v>
+        <v>-1.1297</v>
       </c>
       <c r="G22" t="n">
         <v>-14.513</v>
@@ -2170,13 +2170,13 @@
         <v>17.8401</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.515599999999999</v>
+        <v>-4.4782</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3103000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-6.2052</v>
+        <v>-4.1679</v>
       </c>
       <c r="V22" t="n">
         <v>3.2843</v>
